--- a/t1_confection/A2_Extra_Inputs/A-Xtra_Emissions.xlsx
+++ b/t1_confection/A2_Extra_Inputs/A-Xtra_Emissions.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E138"/>
+  <dimension ref="A1:E286"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="19.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -486,7 +486,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PWRCOAARGXX</t>
+          <t>PWRCCSARGXX</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.2734</v>
+        <v>0.0273</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -509,7 +509,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PWRCOAARGXX</t>
+          <t>PWRCCSARGXX</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.2734</v>
+        <v>0.0273</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -532,16 +532,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PWRCOABRAXX</t>
+          <t>PWRCCSBOLXX</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CO2BRA</t>
+          <t>CO2BOL</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.2752</v>
+        <v>0.0273</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -555,16 +555,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PWRCOABRAXX</t>
+          <t>PWRCCSBOLXX</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CO2BRA</t>
+          <t>CO2BOL</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.2752</v>
+        <v>0.0273</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -578,16 +578,16 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PWRCOACHLXX</t>
+          <t>PWRCCSBRAXX</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CO2CHL</t>
+          <t>CO2BRA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.2743</v>
+        <v>0.0273</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -601,16 +601,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PWRCOACHLXX</t>
+          <t>PWRCCSBRAXX</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CO2CHL</t>
+          <t>CO2BRA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.2743</v>
+        <v>0.0273</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -624,16 +624,16 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PWRCOACOLXX</t>
+          <t>PWRCCSBRBXX</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CO2COL</t>
+          <t>CO2BRB</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.2734</v>
+        <v>0.0273</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -647,16 +647,16 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PWRCOACOLXX</t>
+          <t>PWRCCSBRBXX</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CO2COL</t>
+          <t>CO2BRB</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.2734</v>
+        <v>0.0273</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -670,16 +670,16 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PWRCOADOMXX</t>
+          <t>PWRCCSCHLXX</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CO2DOM</t>
+          <t>CO2CHL</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.2762</v>
+        <v>0.0273</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -693,16 +693,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PWRCOADOMXX</t>
+          <t>PWRCCSCHLXX</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CO2DOM</t>
+          <t>CO2CHL</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.2762</v>
+        <v>0.0273</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -716,16 +716,16 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PWRCOAGTMXX</t>
+          <t>PWRCCSCOLXX</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CO2GTM</t>
+          <t>CO2COL</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.278</v>
+        <v>0.0273</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -739,16 +739,16 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PWRCOAGTMXX</t>
+          <t>PWRCCSCOLXX</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CO2GTM</t>
+          <t>CO2COL</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.278</v>
+        <v>0.0273</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -762,16 +762,16 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PWRCOAMEXXX</t>
+          <t>PWRCCSCRIXX</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CO2MEX</t>
+          <t>CO2CRI</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.2706</v>
+        <v>0.0273</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -785,16 +785,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PWRCOAMEXXX</t>
+          <t>PWRCCSCRIXX</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CO2MEX</t>
+          <t>CO2CRI</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.2706</v>
+        <v>0.0273</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -808,16 +808,16 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PWRCOAPANXX</t>
+          <t>PWRCCSDOMXX</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CO2PAN</t>
+          <t>CO2DOM</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.2771</v>
+        <v>0.0273</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -831,16 +831,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PWRCOAPANXX</t>
+          <t>PWRCCSDOMXX</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CO2PAN</t>
+          <t>CO2DOM</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.2771</v>
+        <v>0.0273</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -854,16 +854,16 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PWRCOAPERXX</t>
+          <t>PWRCCSECUXX</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CO2PER</t>
+          <t>CO2ECU</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.278</v>
+        <v>0.0273</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -877,16 +877,16 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PWRCOAPERXX</t>
+          <t>PWRCCSECUXX</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CO2PER</t>
+          <t>CO2ECU</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.278</v>
+        <v>0.0273</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -900,16 +900,16 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PWRNGSARGXX</t>
+          <t>PWRCCSGTMXX</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CO2ARG</t>
+          <t>CO2GTM</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.12215</v>
+        <v>0.0273</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PWRNGSARGXX</t>
+          <t>PWRCCSGTMXX</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CO2ARG</t>
+          <t>CO2GTM</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.12215</v>
+        <v>0.0273</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -946,16 +946,16 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PWRNGSBOLXX</t>
+          <t>PWRCCSHNDXX</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CO2BOL</t>
+          <t>CO2HND</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.12215</v>
+        <v>0.0273</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -969,16 +969,16 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PWRNGSBOLXX</t>
+          <t>PWRCCSHNDXX</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CO2BOL</t>
+          <t>CO2HND</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.12215</v>
+        <v>0.0273</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PWRNGSBRAXX</t>
+          <t>PWRCCSHTIXX</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CO2BRA</t>
+          <t>CO2HTI</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.12215</v>
+        <v>0.0273</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1015,16 +1015,16 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PWRNGSBRAXX</t>
+          <t>PWRCCSHTIXX</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CO2BRA</t>
+          <t>CO2HTI</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.12215</v>
+        <v>0.0273</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1038,16 +1038,16 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>PWRNGSCHLXX</t>
+          <t>PWRCCSMEXXX</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CO2CHL</t>
+          <t>CO2MEX</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.12215</v>
+        <v>0.0273</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1061,16 +1061,16 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>PWRNGSCHLXX</t>
+          <t>PWRCCSMEXXX</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CO2CHL</t>
+          <t>CO2MEX</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.12215</v>
+        <v>0.0273</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1084,16 +1084,16 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>PWRNGSCOLXX</t>
+          <t>PWRCCSNICXX</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CO2COL</t>
+          <t>CO2NIC</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.12215</v>
+        <v>0.0273</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1107,16 +1107,16 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PWRNGSCOLXX</t>
+          <t>PWRCCSNICXX</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CO2COL</t>
+          <t>CO2NIC</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.12215</v>
+        <v>0.0273</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1130,16 +1130,16 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PWRNGSDOMXX</t>
+          <t>PWRCCSPANXX</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CO2DOM</t>
+          <t>CO2PAN</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.12215</v>
+        <v>0.0273</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1153,16 +1153,16 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PWRNGSDOMXX</t>
+          <t>PWRCCSPANXX</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CO2DOM</t>
+          <t>CO2PAN</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.12215</v>
+        <v>0.0273</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1176,16 +1176,16 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PWRNGSECUXX</t>
+          <t>PWRCCSPERXX</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CO2ECU</t>
+          <t>CO2PER</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.12215</v>
+        <v>0.0273</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1199,16 +1199,16 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>PWRNGSECUXX</t>
+          <t>PWRCCSPERXX</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CO2ECU</t>
+          <t>CO2PER</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.12215</v>
+        <v>0.0273</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1222,16 +1222,16 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PWRNGSGTMXX</t>
+          <t>PWRCCSPRYXX</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CO2GTM</t>
+          <t>CO2PRY</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.12215</v>
+        <v>0.0273</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1245,16 +1245,16 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>PWRNGSGTMXX</t>
+          <t>PWRCCSPRYXX</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CO2GTM</t>
+          <t>CO2PRY</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.12215</v>
+        <v>0.0273</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1268,16 +1268,16 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>PWRNGSMEXXX</t>
+          <t>PWRCCSSLVXX</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CO2MEX</t>
+          <t>CO2SLV</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.12215</v>
+        <v>0.0273</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1291,16 +1291,16 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PWRNGSMEXXX</t>
+          <t>PWRCCSSLVXX</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CO2MEX</t>
+          <t>CO2SLV</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.12215</v>
+        <v>0.0273</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1314,16 +1314,16 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PWRNGSPANXX</t>
+          <t>PWRCCSURYXX</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CO2PAN</t>
+          <t>CO2URY</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.12215</v>
+        <v>0.0273</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1337,16 +1337,16 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PWRNGSPANXX</t>
+          <t>PWRCCSURYXX</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CO2PAN</t>
+          <t>CO2URY</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.12215</v>
+        <v>0.0273</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1360,16 +1360,16 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PWRNGSPERXX</t>
+          <t>PWRCOAARGXX</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CO2PER</t>
+          <t>CO2ARG</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.12215</v>
+        <v>0.2734</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1383,16 +1383,16 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PWRNGSPERXX</t>
+          <t>PWRCOAARGXX</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CO2PER</t>
+          <t>CO2ARG</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.12215</v>
+        <v>0.2734</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1406,16 +1406,16 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PWRNGSSLVXX</t>
+          <t>PWRCOABOLXX</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CO2SLV</t>
+          <t>CO2BOL</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.12215</v>
+        <v>0.2724</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1429,16 +1429,16 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PWRNGSSLVXX</t>
+          <t>PWRCOABOLXX</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CO2SLV</t>
+          <t>CO2BOL</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.12215</v>
+        <v>0.2724</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1452,16 +1452,16 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>PWROILARGXX</t>
+          <t>PWRCOABRAXX</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CO2ARG</t>
+          <t>CO2BRA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.2212</v>
+        <v>0.2752</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1475,16 +1475,16 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PWROILARGXX</t>
+          <t>PWRCOABRAXX</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CO2ARG</t>
+          <t>CO2BRA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.2212</v>
+        <v>0.2752</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1498,16 +1498,16 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>PWROILBOLXX</t>
+          <t>PWRCOABRBXX</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CO2BOL</t>
+          <t>CO2BRB</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.2177</v>
+        <v>0.2724</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1521,16 +1521,16 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PWROILBOLXX</t>
+          <t>PWRCOABRBXX</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CO2BOL</t>
+          <t>CO2BRB</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.2177</v>
+        <v>0.2724</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1544,16 +1544,16 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PWROILBRAXX</t>
+          <t>PWRCOACHLXX</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CO2BRA</t>
+          <t>CO2CHL</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.2223285714285714</v>
+        <v>0.2743</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1567,16 +1567,16 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>PWROILBRAXX</t>
+          <t>PWRCOACHLXX</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CO2BRA</t>
+          <t>CO2CHL</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.2223285714285714</v>
+        <v>0.2743</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -1590,16 +1590,16 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PWROILBRBXX</t>
+          <t>PWRCOACOLXX</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CO2BRB</t>
+          <t>CO2COL</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0.1971</v>
+        <v>0.2734</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -1613,16 +1613,16 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>PWROILBRBXX</t>
+          <t>PWRCOACOLXX</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CO2BRB</t>
+          <t>CO2COL</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.1971</v>
+        <v>0.2734</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -1636,16 +1636,16 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PWROILCHLXX</t>
+          <t>PWRCOACRIXX</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CO2CHL</t>
+          <t>CO2CRI</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.2155</v>
+        <v>0.2724</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -1659,16 +1659,16 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PWROILCHLXX</t>
+          <t>PWRCOACRIXX</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CO2CHL</t>
+          <t>CO2CRI</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.2155</v>
+        <v>0.2724</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -1682,16 +1682,16 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PWROILCOLXX</t>
+          <t>PWRCOADOMXX</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CO2COL</t>
+          <t>CO2DOM</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.195</v>
+        <v>0.2762</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -1705,16 +1705,16 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PWROILCOLXX</t>
+          <t>PWRCOADOMXX</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CO2COL</t>
+          <t>CO2DOM</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.195</v>
+        <v>0.2762</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -1728,16 +1728,16 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PWROILCRIXX</t>
+          <t>PWRCOAECUXX</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>CO2CRI</t>
+          <t>CO2ECU</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.2021</v>
+        <v>0.2724</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -1751,16 +1751,16 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PWROILCRIXX</t>
+          <t>PWRCOAECUXX</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CO2CRI</t>
+          <t>CO2ECU</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.2021</v>
+        <v>0.2724</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -1774,16 +1774,16 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PWROILDOMXX</t>
+          <t>PWRCOAGTMXX</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CO2DOM</t>
+          <t>CO2GTM</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.2042</v>
+        <v>0.278</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -1797,16 +1797,16 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PWROILDOMXX</t>
+          <t>PWRCOAGTMXX</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CO2DOM</t>
+          <t>CO2GTM</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.2042</v>
+        <v>0.278</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -1820,16 +1820,16 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PWROILECUXX</t>
+          <t>PWRCOAHNDXX</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CO2ECU</t>
+          <t>CO2HND</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.2035</v>
+        <v>0.2724</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -1843,16 +1843,16 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PWROILECUXX</t>
+          <t>PWRCOAHNDXX</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CO2ECU</t>
+          <t>CO2HND</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.2035</v>
+        <v>0.2724</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -1866,16 +1866,16 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>PWROILGTMXX</t>
+          <t>PWRCOAHTIXX</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>CO2GTM</t>
+          <t>CO2HTI</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.2092</v>
+        <v>0.2724</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -1889,16 +1889,16 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PWROILGTMXX</t>
+          <t>PWRCOAHTIXX</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CO2GTM</t>
+          <t>CO2HTI</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.2092</v>
+        <v>0.2724</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -1912,16 +1912,16 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PWROILHNDXX</t>
+          <t>PWRCOAMEXXX</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CO2HND</t>
+          <t>CO2MEX</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0.2063</v>
+        <v>0.2706</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -1935,16 +1935,16 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PWROILHNDXX</t>
+          <t>PWRCOAMEXXX</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>CO2HND</t>
+          <t>CO2MEX</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0.2063</v>
+        <v>0.2706</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -1958,16 +1958,16 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PWROILHTIXX</t>
+          <t>PWRCOANICXX</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CO2HTI</t>
+          <t>CO2NIC</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.2177</v>
+        <v>0.2724</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -1981,16 +1981,16 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PWROILHTIXX</t>
+          <t>PWRCOANICXX</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CO2HTI</t>
+          <t>CO2NIC</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0.2177</v>
+        <v>0.2724</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2004,16 +2004,16 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PWROILMEXXX</t>
+          <t>PWRCOAPANXX</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>CO2MEX</t>
+          <t>CO2PAN</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.2042</v>
+        <v>0.2771</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2027,16 +2027,16 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PWROILMEXXX</t>
+          <t>PWRCOAPANXX</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>CO2MEX</t>
+          <t>CO2PAN</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0.2042</v>
+        <v>0.2771</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2050,16 +2050,16 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PWROILNICXX</t>
+          <t>PWRCOAPERXX</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>CO2NIC</t>
+          <t>CO2PER</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0.2063</v>
+        <v>0.278</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2073,16 +2073,16 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PWROILNICXX</t>
+          <t>PWRCOAPERXX</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>CO2NIC</t>
+          <t>CO2PER</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.2063</v>
+        <v>0.278</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2096,16 +2096,16 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PWROILPANXX</t>
+          <t>PWRCOAPRYXX</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>CO2PAN</t>
+          <t>CO2PRY</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>0.2077</v>
+        <v>0.2724</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2119,16 +2119,16 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>PWROILPANXX</t>
+          <t>PWRCOAPRYXX</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CO2PAN</t>
+          <t>CO2PRY</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>0.2077</v>
+        <v>0.2724</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>PWROILPERXX</t>
+          <t>PWRCOASLVXX</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>CO2PER</t>
+          <t>CO2SLV</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>0.2177</v>
+        <v>0.2724</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2165,16 +2165,16 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PWROILPERXX</t>
+          <t>PWRCOASLVXX</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>CO2PER</t>
+          <t>CO2SLV</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0.2177</v>
+        <v>0.2724</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2188,16 +2188,16 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>PWROILPRYXX</t>
+          <t>PWRCOAURYXX</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>CO2PRY</t>
+          <t>CO2URY</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>0.2177</v>
+        <v>0.2724</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2211,16 +2211,16 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>PWROILPRYXX</t>
+          <t>PWRCOAURYXX</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>CO2PRY</t>
+          <t>CO2URY</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0.2177</v>
+        <v>0.2724</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2234,16 +2234,16 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>PWROILSLVXX</t>
+          <t>PWRCOGARGXX</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>CO2SLV</t>
+          <t>CO2ARG</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0.1971</v>
+        <v>0.2724</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2257,16 +2257,16 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>PWROILSLVXX</t>
+          <t>PWRCOGARGXX</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>CO2SLV</t>
+          <t>CO2ARG</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>0.1971</v>
+        <v>0.2724</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2280,16 +2280,16 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>PWROILURYXX</t>
+          <t>PWRCOGBOLXX</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>CO2URY</t>
+          <t>CO2BOL</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>0.2184</v>
+        <v>0.2724</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2303,16 +2303,16 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>PWROILURYXX</t>
+          <t>PWRCOGBOLXX</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>CO2URY</t>
+          <t>CO2BOL</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>0.2184</v>
+        <v>0.2724</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -2326,16 +2326,16 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>PWRPETARGXX</t>
+          <t>PWRCOGBRAXX</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>CO2ARG</t>
+          <t>CO2BRA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0.217</v>
+        <v>0.2724</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -2349,16 +2349,16 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>PWRPETARGXX</t>
+          <t>PWRCOGBRAXX</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>CO2ARG</t>
+          <t>CO2BRA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>0.217</v>
+        <v>0.2724</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -2372,16 +2372,16 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>PWRPETBOLXX</t>
+          <t>PWRCOGBRBXX</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>CO2BOL</t>
+          <t>CO2BRB</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>0.217</v>
+        <v>0.2724</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -2395,16 +2395,16 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>PWRPETBOLXX</t>
+          <t>PWRCOGBRBXX</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>CO2BOL</t>
+          <t>CO2BRB</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>0.217</v>
+        <v>0.2724</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -2418,16 +2418,16 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>PWRPETBRAXX</t>
+          <t>PWRCOGCHLXX</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>CO2BRA</t>
+          <t>CO2CHL</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0.217</v>
+        <v>0.2724</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -2441,16 +2441,16 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>PWRPETBRAXX</t>
+          <t>PWRCOGCHLXX</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>CO2BRA</t>
+          <t>CO2CHL</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>0.217</v>
+        <v>0.2724</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -2464,16 +2464,16 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>PWRPETBRBXX</t>
+          <t>PWRCOGCOLXX</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>CO2BRB</t>
+          <t>CO2COL</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>0.217</v>
+        <v>0.2724</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -2487,16 +2487,16 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>PWRPETBRBXX</t>
+          <t>PWRCOGCOLXX</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>CO2BRB</t>
+          <t>CO2COL</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>0.217</v>
+        <v>0.2724</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -2510,16 +2510,16 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>PWRPETCHLXX</t>
+          <t>PWRCOGCRIXX</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>CO2CHL</t>
+          <t>CO2CRI</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>0.217</v>
+        <v>0.2724</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -2533,16 +2533,16 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>PWRPETCHLXX</t>
+          <t>PWRCOGCRIXX</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>CO2CHL</t>
+          <t>CO2CRI</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>0.217</v>
+        <v>0.2724</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -2556,16 +2556,16 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>PWRPETCOLXX</t>
+          <t>PWRCOGDOMXX</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>CO2COL</t>
+          <t>CO2DOM</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0.217</v>
+        <v>0.2724</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -2579,16 +2579,16 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>PWRPETCOLXX</t>
+          <t>PWRCOGDOMXX</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>CO2COL</t>
+          <t>CO2DOM</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>0.217</v>
+        <v>0.2724</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -2602,16 +2602,16 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>PWRPETCRIXX</t>
+          <t>PWRCOGECUXX</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>CO2CRI</t>
+          <t>CO2ECU</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>0.217</v>
+        <v>0.2724</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -2625,16 +2625,16 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>PWRPETCRIXX</t>
+          <t>PWRCOGECUXX</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>CO2CRI</t>
+          <t>CO2ECU</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>0.217</v>
+        <v>0.2724</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -2648,16 +2648,16 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>PWRPETDOMXX</t>
+          <t>PWRCOGGTMXX</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>CO2DOM</t>
+          <t>CO2GTM</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0.217</v>
+        <v>0.2724</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -2671,16 +2671,16 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>PWRPETDOMXX</t>
+          <t>PWRCOGGTMXX</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>CO2DOM</t>
+          <t>CO2GTM</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0.217</v>
+        <v>0.2724</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -2694,16 +2694,16 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>PWRPETECUXX</t>
+          <t>PWRCOGHNDXX</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>CO2ECU</t>
+          <t>CO2HND</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>0.217</v>
+        <v>0.2724</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -2717,16 +2717,16 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>PWRPETECUXX</t>
+          <t>PWRCOGHNDXX</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>CO2ECU</t>
+          <t>CO2HND</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>0.217</v>
+        <v>0.2724</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -2740,16 +2740,16 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>PWRPETGTMXX</t>
+          <t>PWRCOGHTIXX</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>CO2GTM</t>
+          <t>CO2HTI</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>0.217</v>
+        <v>0.2724</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -2763,16 +2763,16 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>PWRPETGTMXX</t>
+          <t>PWRCOGHTIXX</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>CO2GTM</t>
+          <t>CO2HTI</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>0.217</v>
+        <v>0.2724</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -2786,16 +2786,16 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PWRPETHNDXX</t>
+          <t>PWRCOGMEXXX</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>CO2HND</t>
+          <t>CO2MEX</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0.217</v>
+        <v>0.2724</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -2809,16 +2809,16 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>PWRPETHNDXX</t>
+          <t>PWRCOGMEXXX</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>CO2HND</t>
+          <t>CO2MEX</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>0.217</v>
+        <v>0.2724</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -2832,16 +2832,16 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>PWRPETHTIXX</t>
+          <t>PWRCOGNICXX</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>CO2HTI</t>
+          <t>CO2NIC</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>0.217</v>
+        <v>0.2724</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -2855,16 +2855,16 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>PWRPETHTIXX</t>
+          <t>PWRCOGNICXX</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>CO2HTI</t>
+          <t>CO2NIC</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>0.217</v>
+        <v>0.2724</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -2878,16 +2878,16 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>PWRPETMEXXX</t>
+          <t>PWRCOGPANXX</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>CO2MEX</t>
+          <t>CO2PAN</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>0.217</v>
+        <v>0.2724</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -2901,16 +2901,16 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>PWRPETMEXXX</t>
+          <t>PWRCOGPANXX</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>CO2MEX</t>
+          <t>CO2PAN</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>0.217</v>
+        <v>0.2724</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -2924,16 +2924,16 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>PWRPETNICXX</t>
+          <t>PWRCOGPERXX</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>CO2NIC</t>
+          <t>CO2PER</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>0.217</v>
+        <v>0.2724</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -2947,16 +2947,16 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>PWRPETNICXX</t>
+          <t>PWRCOGPERXX</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>CO2NIC</t>
+          <t>CO2PER</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>0.217</v>
+        <v>0.2724</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -2970,16 +2970,16 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>PWRPETPANXX</t>
+          <t>PWRCOGPRYXX</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>CO2PAN</t>
+          <t>CO2PRY</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>0.217</v>
+        <v>0.2724</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -2993,16 +2993,16 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>PWRPETPANXX</t>
+          <t>PWRCOGPRYXX</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>CO2PAN</t>
+          <t>CO2PRY</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>0.217</v>
+        <v>0.2724</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -3016,16 +3016,16 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>PWRPETPERXX</t>
+          <t>PWRCOGSLVXX</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>CO2PER</t>
+          <t>CO2SLV</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>0.217</v>
+        <v>0.2724</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -3039,16 +3039,16 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>PWRPETPERXX</t>
+          <t>PWRCOGSLVXX</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>CO2PER</t>
+          <t>CO2SLV</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>0.217</v>
+        <v>0.2724</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -3062,16 +3062,16 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>PWRPETPRYXX</t>
+          <t>PWRCOGURYXX</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>CO2PRY</t>
+          <t>CO2URY</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>0.217</v>
+        <v>0.2724</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -3085,16 +3085,16 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>PWRPETPRYXX</t>
+          <t>PWRCOGURYXX</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>CO2PRY</t>
+          <t>CO2URY</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0.217</v>
+        <v>0.2724</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -3108,16 +3108,16 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>PWRPETSLVXX</t>
+          <t>PWRNGSARGXX</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>CO2SLV</t>
+          <t>CO2ARG</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>0.217</v>
+        <v>0.1295</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -3131,16 +3131,16 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>PWRPETSLVXX</t>
+          <t>PWRNGSARGXX</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>CO2SLV</t>
+          <t>CO2ARG</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>0.217</v>
+        <v>0.1295</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -3154,16 +3154,16 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>PWRPETURYXX</t>
+          <t>PWRNGSBOLXX</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>CO2URY</t>
+          <t>CO2BOL</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>0.217</v>
+        <v>0.129</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -3177,16 +3177,16 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>PWRPETURYXX</t>
+          <t>PWRNGSBOLXX</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>CO2URY</t>
+          <t>CO2BOL</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>0.217</v>
+        <v>0.129</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -3200,16 +3200,16 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>PWRWASARGXX</t>
+          <t>PWRNGSBRAXX</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>CO2ARG</t>
+          <t>CO2BRA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>0.08790000000000001</v>
+        <v>0.1321107142857142</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -3219,20 +3219,20 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>PWRWASBOLXX</t>
+          <t>PWRNGSBRAXX</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>CO2BOL</t>
+          <t>CO2BRA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>0.08790000000000001</v>
+        <v>0.1321107142857142</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -3246,16 +3246,16 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>PWRWASBRAXX</t>
+          <t>PWRNGSBRBXX</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>CO2BRA</t>
+          <t>CO2BRB</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>0.08790000000000001</v>
+        <v>0.12735</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -3265,11 +3265,11 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>PWRWASBRBXX</t>
+          <t>PWRNGSBRBXX</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>0.08790000000000001</v>
+        <v>0.12735</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>PWRWASCHLXX</t>
+          <t>PWRNGSCHLXX</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -3301,7 +3301,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>0.08790000000000001</v>
+        <v>0.132625</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -3311,20 +3311,20 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>PWRWASCOLXX</t>
+          <t>PWRNGSCHLXX</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>CO2COL</t>
+          <t>CO2CHL</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>0.08790000000000001</v>
+        <v>0.132625</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -3338,16 +3338,16 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>PWRWASCRIXX</t>
+          <t>PWRNGSCOLXX</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>CO2CRI</t>
+          <t>CO2COL</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>0.08790000000000001</v>
+        <v>0.13075</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -3357,20 +3357,20 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>PWRWASDOMXX</t>
+          <t>PWRNGSCOLXX</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>CO2DOM</t>
+          <t>CO2COL</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>0.08790000000000001</v>
+        <v>0.13075</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -3384,16 +3384,16 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>PWRWASECUXX</t>
+          <t>PWRNGSCRIXX</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>CO2ECU</t>
+          <t>CO2CRI</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>0.08790000000000001</v>
+        <v>0.13075</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -3403,20 +3403,20 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PWRWASGTMXX</t>
+          <t>PWRNGSCRIXX</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>CO2GTM</t>
+          <t>CO2CRI</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>0.08790000000000001</v>
+        <v>0.13075</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -3430,16 +3430,16 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PWRWASHNDXX</t>
+          <t>PWRNGSDOMXX</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>CO2HND</t>
+          <t>CO2DOM</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>0.08790000000000001</v>
+        <v>0.13125</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -3449,20 +3449,20 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PWRWASHTIXX</t>
+          <t>PWRNGSDOMXX</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>CO2HTI</t>
+          <t>CO2DOM</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>0.08790000000000001</v>
+        <v>0.13125</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -3476,16 +3476,16 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PWRWASMEXXX</t>
+          <t>PWRNGSECUXX</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>CO2MEX</t>
+          <t>CO2ECU</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>0.08790000000000001</v>
+        <v>0.1281</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -3495,20 +3495,20 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PWRWASNICXX</t>
+          <t>PWRNGSECUXX</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>CO2NIC</t>
+          <t>CO2ECU</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>0.08790000000000001</v>
+        <v>0.1281</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -3522,16 +3522,16 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PWRWASPANXX</t>
+          <t>PWRNGSGTMXX</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>CO2PAN</t>
+          <t>CO2GTM</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>0.08790000000000001</v>
+        <v>0.13075</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -3541,20 +3541,20 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PWRWASPERXX</t>
+          <t>PWRNGSGTMXX</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>CO2PER</t>
+          <t>CO2GTM</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>0.08790000000000001</v>
+        <v>0.13075</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -3568,16 +3568,16 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>PWRWASPRYXX</t>
+          <t>PWRNGSHNDXX</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>CO2PRY</t>
+          <t>CO2HND</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>0.08790000000000001</v>
+        <v>0.1305</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -3587,20 +3587,20 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>PWRWASSLVXX</t>
+          <t>PWRNGSHNDXX</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>CO2SLV</t>
+          <t>CO2HND</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>0.08790000000000001</v>
+        <v>0.1305</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -3614,18 +3614,3422 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
+          <t>PWRNGSHTIXX</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>CO2HTI</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>0.13075</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>2</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>PWRNGSHTIXX</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>CO2HTI</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>0.13075</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>1</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>PWRNGSMEXXX</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>CO2MEX</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>0.127225</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>2</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>PWRNGSMEXXX</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>CO2MEX</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>0.127225</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>1</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>PWRNGSNICXX</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>CO2NIC</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>0.1256</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>2</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>PWRNGSNICXX</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>CO2NIC</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>0.1256</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>1</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>PWRNGSPANXX</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>CO2PAN</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>0.129475</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>2</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>PWRNGSPANXX</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>CO2PAN</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>0.129475</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>1</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>PWRNGSPERXX</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>CO2PER</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>0.1286</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>2</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>PWRNGSPERXX</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>CO2PER</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>0.1286</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>1</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>PWRNGSPRYXX</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>CO2PRY</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>0.13075</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>2</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>PWRNGSPRYXX</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>CO2PRY</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>0.13075</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>1</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>PWRNGSSLVXX</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>CO2SLV</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>0.13075</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>2</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>PWRNGSSLVXX</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>CO2SLV</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>0.13075</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>1</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>PWRNGSURYXX</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>CO2URY</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>0.131375</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>2</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>PWRNGSURYXX</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>CO2URY</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>0.131375</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>1</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>PWROILARGXX</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>CO2ARG</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>0.2212</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>2</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>PWROILARGXX</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>CO2ARG</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>0.2212</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>1</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>PWROILBOLXX</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>CO2BOL</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>0.2177</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>2</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>PWROILBOLXX</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>CO2BOL</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>0.2177</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>1</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>PWROILBRAXX</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>CO2BRA</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>0.2223285714285714</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>2</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>PWROILBRAXX</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>CO2BRA</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>0.2223285714285714</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>1</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>PWROILBRBXX</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>CO2BRB</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>0.1971</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>2</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>PWROILBRBXX</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>CO2BRB</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>0.1971</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>1</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>PWROILCHLXX</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>CO2CHL</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>0.2155</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>2</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>PWROILCHLXX</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>CO2CHL</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>0.2155</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>1</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>PWROILCOLXX</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>CO2COL</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>2</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>PWROILCOLXX</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>CO2COL</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>1</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>PWROILCRIXX</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>CO2CRI</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>0.2021</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>2</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>PWROILCRIXX</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>CO2CRI</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>0.2021</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>1</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>PWROILDOMXX</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>CO2DOM</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>0.2042</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>2</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>PWROILDOMXX</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>CO2DOM</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>0.2042</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>1</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>PWROILECUXX</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>CO2ECU</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>0.2035</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>2</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>PWROILECUXX</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>CO2ECU</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>0.2035</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>1</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>PWROILGTMXX</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>CO2GTM</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>0.2092</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>2</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>PWROILGTMXX</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>CO2GTM</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>0.2092</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>1</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>PWROILHNDXX</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>CO2HND</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>0.2063</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>2</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>PWROILHNDXX</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>CO2HND</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>0.2063</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>1</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>PWROILHTIXX</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>CO2HTI</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>0.2177</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>2</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>PWROILHTIXX</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>CO2HTI</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>0.2177</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>1</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>PWROILMEXXX</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>CO2MEX</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>0.2042</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>2</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>PWROILMEXXX</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>CO2MEX</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>0.2042</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>1</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>PWROILNICXX</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>CO2NIC</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>0.2063</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>2</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>PWROILNICXX</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>CO2NIC</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>0.2063</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>1</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>PWROILPANXX</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>CO2PAN</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>0.2077</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>2</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>PWROILPANXX</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>CO2PAN</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>0.2077</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>1</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>PWROILPERXX</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>CO2PER</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>0.2177</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>2</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>PWROILPERXX</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>CO2PER</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>0.2177</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>1</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>PWROILPRYXX</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>CO2PRY</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>0.2177</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>2</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>PWROILPRYXX</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>CO2PRY</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>0.2177</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>1</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>PWROILSLVXX</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>CO2SLV</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>0.1971</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>2</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>PWROILSLVXX</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>CO2SLV</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>0.1971</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>1</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>PWROILURYXX</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>CO2URY</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>0.2184</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>2</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>PWROILURYXX</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>CO2URY</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>0.2184</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>1</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>PWROTHARGXX</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>CO2ARG</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>0.0503</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>2</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>PWROTHARGXX</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>CO2ARG</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>0.0503</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>1</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>PWROTHBOLXX</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>CO2BOL</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>0.0503</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>2</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>PWROTHBOLXX</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>CO2BOL</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>0.0503</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>1</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>PWROTHBRAXX</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>CO2BRA</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>0.0503</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>2</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>PWROTHBRAXX</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>CO2BRA</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>0.0503</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>1</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>PWROTHBRBXX</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>CO2BRB</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>0.0503</v>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>2</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>PWROTHBRBXX</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>CO2BRB</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>0.0503</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>1</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>PWROTHCHLXX</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>CO2CHL</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>0.0503</v>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>2</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>PWROTHCHLXX</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>CO2CHL</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>0.0503</v>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>1</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>PWROTHCOLXX</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>CO2COL</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>0.0503</v>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>2</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>PWROTHCOLXX</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>CO2COL</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>0.0503</v>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>1</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>PWROTHCRIXX</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>CO2CRI</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>0.0503</v>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>2</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>PWROTHCRIXX</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>CO2CRI</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>0.0503</v>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>1</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>PWROTHDOMXX</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>CO2DOM</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>0.0503</v>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>2</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>PWROTHDOMXX</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>CO2DOM</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>0.0503</v>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>1</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>PWROTHECUXX</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>CO2ECU</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>0.0503</v>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>2</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>PWROTHECUXX</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>CO2ECU</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>0.0503</v>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>1</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>PWROTHGTMXX</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>CO2GTM</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>0.0503</v>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>2</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>PWROTHGTMXX</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>CO2GTM</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>0.0503</v>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>1</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>PWROTHHNDXX</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>CO2HND</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>0.0503</v>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>2</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>PWROTHHNDXX</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>CO2HND</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>0.0503</v>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>1</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>PWROTHHTIXX</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>CO2HTI</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>0.0503</v>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>2</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>PWROTHHTIXX</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>CO2HTI</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>0.0503</v>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>1</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>PWROTHMEXXX</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>CO2MEX</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>0.0503</v>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>2</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>PWROTHMEXXX</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>CO2MEX</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>0.0503</v>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>1</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>PWROTHNICXX</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>CO2NIC</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>0.0503</v>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>2</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>PWROTHNICXX</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>CO2NIC</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>0.0503</v>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>1</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>PWROTHPANXX</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>CO2PAN</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>0.0503</v>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>2</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>PWROTHPANXX</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>CO2PAN</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>0.0503</v>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>1</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>PWROTHPERXX</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>CO2PER</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>0.0503</v>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>2</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>PWROTHPERXX</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>CO2PER</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>0.0503</v>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>1</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>PWROTHPRYXX</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>CO2PRY</t>
+        </is>
+      </c>
+      <c r="D224" t="n">
+        <v>0.0503</v>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>2</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>PWROTHPRYXX</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>CO2PRY</t>
+        </is>
+      </c>
+      <c r="D225" t="n">
+        <v>0.0503</v>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>1</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>PWROTHSLVXX</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>CO2SLV</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>0.0503</v>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>2</v>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>PWROTHSLVXX</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>CO2SLV</t>
+        </is>
+      </c>
+      <c r="D227" t="n">
+        <v>0.0503</v>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>1</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>PWROTHURYXX</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>CO2URY</t>
+        </is>
+      </c>
+      <c r="D228" t="n">
+        <v>0.0503</v>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>2</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>PWROTHURYXX</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>CO2URY</t>
+        </is>
+      </c>
+      <c r="D229" t="n">
+        <v>0.0503</v>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>1</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>PWRPETARGXX</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>CO2ARG</t>
+        </is>
+      </c>
+      <c r="D230" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>2</v>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>PWRPETARGXX</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>CO2ARG</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>1</v>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>PWRPETBOLXX</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>CO2BOL</t>
+        </is>
+      </c>
+      <c r="D232" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>2</v>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>PWRPETBOLXX</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>CO2BOL</t>
+        </is>
+      </c>
+      <c r="D233" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>1</v>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>PWRPETBRAXX</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>CO2BRA</t>
+        </is>
+      </c>
+      <c r="D234" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>2</v>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>PWRPETBRAXX</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>CO2BRA</t>
+        </is>
+      </c>
+      <c r="D235" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>1</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>PWRPETBRBXX</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>CO2BRB</t>
+        </is>
+      </c>
+      <c r="D236" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>2</v>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>PWRPETBRBXX</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>CO2BRB</t>
+        </is>
+      </c>
+      <c r="D237" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>1</v>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>PWRPETCHLXX</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>CO2CHL</t>
+        </is>
+      </c>
+      <c r="D238" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>2</v>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>PWRPETCHLXX</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>CO2CHL</t>
+        </is>
+      </c>
+      <c r="D239" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>1</v>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>PWRPETCOLXX</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>CO2COL</t>
+        </is>
+      </c>
+      <c r="D240" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>2</v>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>PWRPETCOLXX</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>CO2COL</t>
+        </is>
+      </c>
+      <c r="D241" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>1</v>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>PWRPETCRIXX</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>CO2CRI</t>
+        </is>
+      </c>
+      <c r="D242" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>2</v>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>PWRPETCRIXX</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>CO2CRI</t>
+        </is>
+      </c>
+      <c r="D243" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>1</v>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>PWRPETDOMXX</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>CO2DOM</t>
+        </is>
+      </c>
+      <c r="D244" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>2</v>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>PWRPETDOMXX</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>CO2DOM</t>
+        </is>
+      </c>
+      <c r="D245" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>1</v>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>PWRPETECUXX</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>CO2ECU</t>
+        </is>
+      </c>
+      <c r="D246" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>2</v>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>PWRPETECUXX</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>CO2ECU</t>
+        </is>
+      </c>
+      <c r="D247" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>1</v>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>PWRPETGTMXX</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>CO2GTM</t>
+        </is>
+      </c>
+      <c r="D248" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>2</v>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>PWRPETGTMXX</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>CO2GTM</t>
+        </is>
+      </c>
+      <c r="D249" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>1</v>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>PWRPETHNDXX</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>CO2HND</t>
+        </is>
+      </c>
+      <c r="D250" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>2</v>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>PWRPETHNDXX</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>CO2HND</t>
+        </is>
+      </c>
+      <c r="D251" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>1</v>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>PWRPETHTIXX</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>CO2HTI</t>
+        </is>
+      </c>
+      <c r="D252" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>2</v>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>PWRPETHTIXX</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>CO2HTI</t>
+        </is>
+      </c>
+      <c r="D253" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>1</v>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>PWRPETMEXXX</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>CO2MEX</t>
+        </is>
+      </c>
+      <c r="D254" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>2</v>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>PWRPETMEXXX</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>CO2MEX</t>
+        </is>
+      </c>
+      <c r="D255" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>1</v>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>PWRPETNICXX</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>CO2NIC</t>
+        </is>
+      </c>
+      <c r="D256" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>2</v>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>PWRPETNICXX</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>CO2NIC</t>
+        </is>
+      </c>
+      <c r="D257" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>1</v>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>PWRPETPANXX</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>CO2PAN</t>
+        </is>
+      </c>
+      <c r="D258" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>2</v>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>PWRPETPANXX</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>CO2PAN</t>
+        </is>
+      </c>
+      <c r="D259" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>1</v>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>PWRPETPERXX</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>CO2PER</t>
+        </is>
+      </c>
+      <c r="D260" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>2</v>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>PWRPETPERXX</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>CO2PER</t>
+        </is>
+      </c>
+      <c r="D261" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>1</v>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>PWRPETPRYXX</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>CO2PRY</t>
+        </is>
+      </c>
+      <c r="D262" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>2</v>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>PWRPETPRYXX</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>CO2PRY</t>
+        </is>
+      </c>
+      <c r="D263" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>1</v>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>PWRPETSLVXX</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>CO2SLV</t>
+        </is>
+      </c>
+      <c r="D264" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>2</v>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>PWRPETSLVXX</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>CO2SLV</t>
+        </is>
+      </c>
+      <c r="D265" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>1</v>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>PWRPETURYXX</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>CO2URY</t>
+        </is>
+      </c>
+      <c r="D266" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>2</v>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>PWRPETURYXX</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>CO2URY</t>
+        </is>
+      </c>
+      <c r="D267" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>1</v>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>PWRWASARGXX</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>CO2ARG</t>
+        </is>
+      </c>
+      <c r="D268" t="n">
+        <v>0.08790000000000001</v>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>1</v>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>PWRWASBOLXX</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>CO2BOL</t>
+        </is>
+      </c>
+      <c r="D269" t="n">
+        <v>0.08790000000000001</v>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>1</v>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>PWRWASBRAXX</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>CO2BRA</t>
+        </is>
+      </c>
+      <c r="D270" t="n">
+        <v>0.08790000000000001</v>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>1</v>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>PWRWASBRBXX</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>CO2BRB</t>
+        </is>
+      </c>
+      <c r="D271" t="n">
+        <v>0.08790000000000001</v>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>1</v>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>PWRWASCHLXX</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>CO2CHL</t>
+        </is>
+      </c>
+      <c r="D272" t="n">
+        <v>0.08790000000000001</v>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>1</v>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>PWRWASCOLXX</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>CO2COL</t>
+        </is>
+      </c>
+      <c r="D273" t="n">
+        <v>0.08790000000000001</v>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>1</v>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>PWRWASCRIXX</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>CO2CRI</t>
+        </is>
+      </c>
+      <c r="D274" t="n">
+        <v>0.08790000000000001</v>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>1</v>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>PWRWASDOMXX</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>CO2DOM</t>
+        </is>
+      </c>
+      <c r="D275" t="n">
+        <v>0.08790000000000001</v>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>1</v>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>PWRWASECUXX</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>CO2ECU</t>
+        </is>
+      </c>
+      <c r="D276" t="n">
+        <v>0.08790000000000001</v>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>1</v>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>PWRWASGTMXX</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>CO2GTM</t>
+        </is>
+      </c>
+      <c r="D277" t="n">
+        <v>0.08790000000000001</v>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>1</v>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>PWRWASHNDXX</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>CO2HND</t>
+        </is>
+      </c>
+      <c r="D278" t="n">
+        <v>0.08790000000000001</v>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>1</v>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>PWRWASHTIXX</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>CO2HTI</t>
+        </is>
+      </c>
+      <c r="D279" t="n">
+        <v>0.08790000000000001</v>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>1</v>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>PWRWASMEXXX</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>CO2MEX</t>
+        </is>
+      </c>
+      <c r="D280" t="n">
+        <v>0.08790000000000001</v>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>1</v>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>PWRWASNICXX</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>CO2NIC</t>
+        </is>
+      </c>
+      <c r="D281" t="n">
+        <v>0.08790000000000001</v>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>1</v>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>PWRWASPANXX</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>CO2PAN</t>
+        </is>
+      </c>
+      <c r="D282" t="n">
+        <v>0.08790000000000001</v>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>1</v>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>PWRWASPERXX</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>CO2PER</t>
+        </is>
+      </c>
+      <c r="D283" t="n">
+        <v>0.08790000000000001</v>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>1</v>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>PWRWASPRYXX</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>CO2PRY</t>
+        </is>
+      </c>
+      <c r="D284" t="n">
+        <v>0.08790000000000001</v>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>1</v>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>PWRWASSLVXX</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>CO2SLV</t>
+        </is>
+      </c>
+      <c r="D285" t="n">
+        <v>0.08790000000000001</v>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>1</v>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
           <t>PWRWASURYXX</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr">
+      <c r="C286" t="inlineStr">
         <is>
           <t>CO2URY</t>
         </is>
       </c>
-      <c r="D138" t="n">
+      <c r="D286" t="n">
         <v>0.08790000000000001</v>
       </c>
-      <c r="E138" t="inlineStr">
+      <c r="E286" t="inlineStr">
         <is>
           <t>MT</t>
         </is>
